--- a/stories/arbres/ATOM-LAN.SON.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom s'assoit près de la fenêtre avec maman. Il pleut. Plic ploc. Maman dit : c'est un son. Quel nom ? Tom dit : la pluie. Un bruit long : tchou tchou. Tom dit le nom : le train. Puis, un miaulement. Tom dit : le chat. Maman dit : on entend un son. On dit le nom. Pluie. Train. Chat.</t>
+          <t>Tom s'assoit près de la fenêtre avec maman. Il pleut. Plic ploc. C'est un son. Quel nom ? La pluie. Un bruit long : tchou tchou. Tom dit le nom : le train. Puis, un miaulement. Le chat. On entend un son. On dit le nom. Pluie. Train. Chat.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit près de la fenêtre avec maman. Il pleut. Plic ploc.
+maman|C'est un son. Quel nom ?
+enfant-m|La pluie.
+narrateur|Un bruit long : tchou tchou. Tom dit le nom : le train. Puis, un miaulement.
+enfant-m|Le chat.
+maman|On entend un son. On dit le nom. Pluie. Train. Chat.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Tom entend un bruit. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a entendu un son. Il a dit le nom. Pluie. Train. Chat.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat vient. Tom le caresse.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 maman|On entend un son. On dit le nom. Pluie. Train. Chat.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Tom entend un bruit. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Tom a entendu un son. Il a dit le nom. Pluie. Train. Chat.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Le chat vient. Tom le caresse.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.SON.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tom nomme les sons de la fenêtre</t>
+          <t>Le rayon du tapis de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rayon barre le tapis. Nino s'assoit près de la fenêtre. Il nomme la pluie, le train, le chat. Puis le chat vient.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom s'assoit près de la fenêtre avec maman. Il pleut. Plic ploc. C'est un son. Quel nom ? La pluie. Un bruit long : tchou tchou. Tom dit le nom : le train. Puis, un miaulement. Le chat. On entend un son. On dit le nom. Pluie. Train. Chat.</t>
+          <t>Un rayon de lumière barre le tapis du salon. Le coussin rouge est tout chaud. Dehors, le ciel est gris. La pendule fait un petit tic. Ça sent le pain, plus loin. Un livre ouvert attend sur la table basse. Les pages sont un peu gondolées. Une chaussette rouge traîne sous le canapé. Le tapis est doux, Nino. Tu prends le coussin ? Oui, maman. Il est chaud. Je coupe le pain, là-bas. Je vous écoute. En ce moment, Nino s'assoit près de la fenêtre. Il pleut. Plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Un bruit long arrive. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. On entend un son. On dit le nom. Pluie. Train. Chat. Bravo, Nino. Tu as nommé le son. C'est du bon travail. Tu restes près de la fenêtre ? Oui, maman. Le rayon a bougé un peu. Il touche maintenant le coussin. La pendule reprend son tic. Tu as entendu trois sons. Pluie, train, chat. Tu as dit le nom.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Tom s'assoit près de la fenêtre avec maman. Il pleut. Plic ploc.
-maman|C'est un son. Quel nom ?
+          <t>narrateur|Un rayon de lumière barre le tapis du salon.
+narrateur|Le coussin rouge est tout chaud.
+narrateur|Dehors, le ciel est gris.
+narrateur|La pendule fait un petit tic.
+narrateur|Ça sent le pain, plus loin.
+narrateur|Un livre ouvert attend sur la table basse.
+narrateur|Les pages sont un peu gondolées.
+narrateur|Une chaussette rouge traîne sous le canapé.
+maman|Le tapis est doux, Nino.
+maman|Tu prends le coussin ?
+enfant-m|Oui, maman.
+enfant-m|Il est chaud.
+papa|Je coupe le pain, là-bas.
+papa|Je vous écoute.
+narrateur|En ce moment, Nino s'assoit près de la fenêtre.
+narrateur|Il pleut.
+narrateur|Plic ploc.
+maman|C'est un son.
+maman|Quel nom ?
 enfant-m|La pluie.
-narrateur|Un bruit long : tchou tchou. Tom dit le nom : le train. Puis, un miaulement.
+maman|Oui.
+maman|Le nom du son, c'est la pluie.
+narrateur|Un bruit long arrive.
+narrateur|Tchou tchou.
+maman|Encore un son.
+maman|Quel nom ?
+enfant-m|Le train.
+maman|Oui.
+maman|Le nom du son, c'est le train.
+narrateur|Puis, un miaulement.
+narrateur|Miaou.
+maman|Un son.
+maman|Quel nom ?
 enfant-m|Le chat.
-maman|On entend un son. On dit le nom. Pluie. Train. Chat.</t>
+maman|Oui.
+maman|On entend un son.
+maman|On dit le nom.
+enfant-m|Pluie.
+enfant-m|Train.
+enfant-m|Chat.
+papa|Bravo, Nino.
+papa|Tu as nommé le son.
+maman|C'est du bon travail.
+maman|Tu restes près de la fenêtre ?
+enfant-m|Oui, maman.
+narrateur|Le rayon a bougé un peu.
+narrateur|Il touche maintenant le coussin.
+narrateur|La pendule reprend son tic.
+maman|Tu as entendu trois sons.
+enfant-m|Pluie, train, chat.
+papa|Tu as dit le nom.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1345,7 +1402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tom entend un bruit. C'est quoi ?</t>
+          <t>Nino entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Tom entend un bruit. C'est quoi ?</t>
+          <t>narrateur|Nino entend un bruit.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom a entendu un son. Il a dit le nom. Pluie. Train. Chat.</t>
+          <t>Nino a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. C'est du bon travail, Nino. Le chat vient ? On va voir.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1731,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tom a entendu un son. Il a dit le nom. Pluie. Train. Chat.</t>
+          <t>narrateur|Nino a entendu un son.
+narrateur|Il a dit le nom.
+maman|Pluie.
+maman|Train.
+maman|Chat.
+maman|Bravo.
+papa|Tu as nommé le son.
+papa|C'est du bon travail, Nino.
+enfant-m|Le chat vient ?
+maman|On va voir.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le chat vient. Tom le caresse.</t>
+          <t>Le chat vient. Nino le caresse. Le poil est doux, un peu chaud. Il aime ça, le chat. Il ronronne. C'est encore un son. Tu as dit le nom. Le chat. Oui. Bravo, Nino. Le livre reste ouvert sur la table. Le rayon glisse vers le canapé. Le pain est prêt, après.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,7 +1904,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le chat vient. Tom le caresse.</t>
+          <t>narrateur|Le chat vient.
+narrateur|Nino le caresse.
+narrateur|Le poil est doux, un peu chaud.
+maman|Il aime ça, le chat.
+enfant-m|Il ronronne.
+papa|C'est encore un son.
+papa|Tu as dit le nom.
+enfant-m|Le chat.
+maman|Oui.
+maman|Bravo, Nino.
+narrateur|Le livre reste ouvert sur la table.
+narrateur|Le rayon glisse vers le canapé.
+papa|Le pain est prêt, après.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1865,7 +1944,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Nino. Tu as fait du bon travail. Le rayon s'est endormi sur le tapis. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,7 +2084,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai entendu un son.
+enfant-m|J'ai dit le nom.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Le rayon s'est endormi sur le tapis.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2027,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2149,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon de lumière barre le tapis du salon. Le coussin rouge est tout chaud. Dehors, le ciel est gris. La pendule fait un petit tic. Ça sent le pain, plus loin. Un livre ouvert attend sur la table basse. Les pages sont un peu gondolées. Une chaussette rouge traîne sous le canapé. Le tapis est doux, Nino. Tu prends le coussin ? Oui, maman. Il est chaud. Je coupe le pain, là-bas. Je vous écoute. En ce moment, Nino s'assoit près de la fenêtre. Il pleut. Plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Un bruit long arrive. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. On entend un son. On dit le nom. Pluie. Train. Chat. Bravo, Nino. Tu as nommé le son. C'est du bon travail. Tu restes près de la fenêtre ? Oui, maman. Le rayon a bougé un peu. Il touche maintenant le coussin. La pendule reprend son tic. Tu as entendu trois sons. Pluie, train, chat. Tu as dit le nom.</t>
+          <t>Un rayon de lumière barre le tapis du salon. Le coussin rouge est tout chaud. Dehors, le ciel est gris. La pendule fait un petit tic. Ça sent le pain, plus loin. Un livre ouvert attend sur la table basse. Les pages sont un peu gondolées. Une chaussette rouge traîne sous le canapé. Le tapis est doux, Nino. Tu prends le coussin ? Oui, maman. Il est chaud. Je coupe le pain, là-bas. Je vous écoute. En ce moment, Nino s'assoit près de la fenêtre. Il pleut. Plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Un bruit long arrive. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. On entend un son. On dit le nom. Pluie. Train. Chat. Bravo, Nino. Tu as nommé le son. Tu restes près de la fenêtre ? Oui, maman. Le rayon a bougé un peu. Il touche maintenant le coussin. La pendule reprend son tic. Tu as entendu trois sons. Pluie, train, chat. Tu as dit le nom.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tom s'assoit près de la fenêtre avec maman. Il pleut. Plic ploc. Maman dit : c'est un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Quel nom ? Tom dit : la pluie. Un bruit long : tchou tchou. Tom dit le nom : le train. Puis, un miaulement. Tom dit : le chat. Maman dit : on entend un son. On dit le nom. Pluie. Train. Chat.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon de lumière barre le tapis du salon. Le coussin rouge est tout chaud. Dehors, le ciel est gris. La pendule fait un petit tic. Ça sent le pain, plus loin. Un livre ouvert attend sur la table basse. Les pages sont un peu gondolées. Une chaussette rouge traîne sous le canapé. Le tapis est doux, Nino. Tu prends le coussin ? Oui, maman. Il est chaud. Je coupe le pain, là-bas. Je vous écoute. En ce moment, Nino s'assoit près de la fenêtre. Il pleut. Plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Un bruit long arrive. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. On entend un son. On dit le nom. Pluie. Train. Chat. Bravo, Nino. Tu as nommé le son. Tu restes près de la fenêtre ? Oui, maman. Le rayon a bougé un peu. Il touche maintenant le coussin. La pendule reprend son tic. Tu as entendu trois sons. Pluie, train, chat. Tu as dit le nom.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 enfant-m|Chat.
 papa|Bravo, Nino.
 papa|Tu as nommé le son.
-maman|C'est du bon travail.
 maman|Tu restes près de la fenêtre ?
 enfant-m|Oui, maman.
 narrateur|Le rayon a bougé un peu.
@@ -1377,7 +1376,6 @@
 papa|Tu as dit le nom.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1407,7 +1405,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tom entend un bruit. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1562,7 +1560,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1587,12 +1584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. C'est du bon travail, Nino. Le chat vient ? On va voir.</t>
+          <t>Nino a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. Le chat vient ? On va voir.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tom a entendu un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Il a dit le nom. Pluie. Train. Chat.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. Le chat vient ? On va voir.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1738,12 +1735,10 @@
 maman|Chat.
 maman|Bravo.
 papa|Tu as nommé le son.
-papa|C'est du bon travail, Nino.
 enfant-m|Le chat vient ?
 maman|On va voir.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le chat vient. Tom le caresse.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat vient. Nino le caresse. Le poil est doux, un peu chaud. Il aime ça, le chat. Il ronronne. C'est encore un son. Tu as dit le nom. Le chat. Oui. Bravo, Nino. Le livre reste ouvert sur la table. Le rayon glisse vers le canapé. Le pain est prêt, après.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1919,7 +1914,6 @@
 papa|Le pain est prêt, après.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1944,12 +1938,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Nino. Tu as fait du bon travail. Le rayon s'est endormi sur le tapis. L'histoire est finie.</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Nino. Le rayon s'est endormi sur le tapis.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Nino. Le rayon s'est endormi sur le tapis.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2087,12 +2081,9 @@
           <t>enfant-m|J'ai entendu un son.
 enfant-m|J'ai dit le nom.
 maman|Bravo, Nino.
-papa|Tu as fait du bon travail.
-narrateur|Le rayon s'est endormi sur le tapis.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le rayon s'est endormi sur le tapis.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2111,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2147,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tom, maman</t>
+          <t>Nino, maman, papa</t>
         </is>
       </c>
     </row>
